--- a/Data_Table/쥐 등급 테이블.xlsx
+++ b/Data_Table/쥐 등급 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,10 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +484,26 @@
           <t>기본 공격력</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>승급 시작 마릿수</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>승급 증가율</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>승급 완화 시작 마릿수</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>승급 완화 증가율</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -527,6 +551,26 @@
           <t>atk_base</t>
         </is>
       </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>promote_base</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>promote_grow</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>promote_soft</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>promote_grow2</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -574,6 +618,26 @@
           <t>int</t>
         </is>
       </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -609,6 +673,18 @@
       <c r="I4" s="1" t="n">
         <v>10</v>
       </c>
+      <c r="J4" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>1.05</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -636,13 +712,25 @@
         <v>8</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1.3</v>
+        <v>0.83</v>
       </c>
       <c r="H5" s="1" t="n">
         <v>1.5</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>15</v>
+        <v>18</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="6">
@@ -671,13 +759,25 @@
         <v>1</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>1.7</v>
+        <v>0.66</v>
       </c>
       <c r="H6" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>21</v>
+        <v>32</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="7">
@@ -706,13 +806,25 @@
         <v>0.1</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>2.2</v>
+        <v>0.52</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>0.8</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>30</v>
+        <v>58</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="8">
@@ -741,13 +853,25 @@
         <v>0.01</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>3</v>
+        <v>0.42</v>
       </c>
       <c r="H8" s="1" t="n">
         <v>0.6</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>44</v>
+        <v>105</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1.05</v>
       </c>
     </row>
     <row r="9">
@@ -776,13 +900,25 @@
         <v>0.00186</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>4</v>
+        <v>0.34</v>
       </c>
       <c r="H9" s="1" t="n">
         <v>0.5</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>64</v>
+        <v>189</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Data_Table/쥐 등급 테이블.xlsx
+++ b/Data_Table/쥐 등급 테이블.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -451,55 +451,60 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>등급 이름 키</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>색상</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>크기 배율</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>이동 속도 배율</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>탄생 가중치</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>스킬 위력 배율</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>조각 계수</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>기본 공격력</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>승급 시작 마릿수</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>승급 증가율</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>승급 완화 시작 마릿수</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>승급 완화 증가율</t>
         </is>
@@ -518,55 +523,60 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
+          <t>grade_name_sk</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
           <t>color</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>size</t>
         </is>
       </c>
-      <c r="E2" s="1" t="inlineStr">
+      <c r="F2" s="1" t="inlineStr">
         <is>
           <t>move_speed</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>birth_weight</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>skill_power</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>shard_k</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>atk_base</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>promote_base</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>promote_grow</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>promote_soft</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>promote_grow2</t>
         </is>
@@ -585,55 +595,60 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="L3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="L3" s="1" t="inlineStr">
+      <c r="M3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="M3" s="1" t="inlineStr">
+      <c r="N3" s="1" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -650,39 +665,42 @@
           <t>일반</t>
         </is>
       </c>
-      <c r="C4" s="1" t="inlineStr">
+      <c r="C4" s="1" t="n">
+        <v>1800001</v>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>#a8a29a</t>
         </is>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>1</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>1</v>
       </c>
       <c r="F4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>100</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="H4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="1" t="n">
+      <c r="I4" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="J4" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="J4" s="1" t="n">
+      <c r="K4" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="K4" s="1" t="n">
+      <c r="L4" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="L4" s="1" t="n">
+      <c r="M4" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M4" s="1" t="n">
+      <c r="N4" s="1" t="n">
         <v>1.05</v>
       </c>
     </row>
@@ -697,39 +715,42 @@
           <t>레어</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="C5" s="1" t="n">
+        <v>1800002</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>#7fa8bf</t>
         </is>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="E5" s="1" t="n">
         <v>1.12</v>
       </c>
-      <c r="E5" s="1" t="n">
+      <c r="F5" s="1" t="n">
         <v>1.05</v>
       </c>
-      <c r="F5" s="1" t="n">
+      <c r="G5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="H5" s="1" t="n">
         <v>0.83</v>
       </c>
-      <c r="H5" s="1" t="n">
+      <c r="I5" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="I5" s="1" t="n">
+      <c r="J5" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="K5" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="L5" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="L5" s="1" t="n">
+      <c r="M5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M5" s="1" t="n">
+      <c r="N5" s="1" t="n">
         <v>1.05</v>
       </c>
     </row>
@@ -744,39 +765,42 @@
           <t>에픽</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C6" s="1" t="n">
+        <v>1800003</v>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
         <is>
           <t>#a58bb8</t>
         </is>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="E6" s="1" t="n">
         <v>1.25</v>
       </c>
-      <c r="E6" s="1" t="n">
+      <c r="F6" s="1" t="n">
         <v>1.1</v>
       </c>
-      <c r="F6" s="1" t="n">
+      <c r="G6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="H6" s="1" t="n">
         <v>0.66</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="I6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="1" t="n">
+      <c r="J6" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="K6" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="L6" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="L6" s="1" t="n">
+      <c r="M6" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M6" s="1" t="n">
+      <c r="N6" s="1" t="n">
         <v>1.05</v>
       </c>
     </row>
@@ -791,39 +815,42 @@
           <t>유니크</t>
         </is>
       </c>
-      <c r="C7" s="1" t="inlineStr">
+      <c r="C7" s="1" t="n">
+        <v>1800004</v>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>#c9846e</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="E7" s="1" t="n">
         <v>1.4</v>
       </c>
-      <c r="E7" s="1" t="n">
+      <c r="F7" s="1" t="n">
         <v>1.15</v>
       </c>
-      <c r="F7" s="1" t="n">
+      <c r="G7" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="H7" s="1" t="n">
         <v>0.52</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="I7" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="I7" s="1" t="n">
+      <c r="J7" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="K7" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="K7" s="1" t="n">
+      <c r="L7" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="L7" s="1" t="n">
+      <c r="M7" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M7" s="1" t="n">
+      <c r="N7" s="1" t="n">
         <v>1.05</v>
       </c>
     </row>
@@ -838,39 +865,42 @@
           <t>전설</t>
         </is>
       </c>
-      <c r="C8" s="1" t="inlineStr">
+      <c r="C8" s="1" t="n">
+        <v>1800005</v>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
         <is>
           <t>#d9a441</t>
         </is>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="E8" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="E8" s="1" t="n">
+      <c r="F8" s="1" t="n">
         <v>1.1</v>
       </c>
-      <c r="F8" s="1" t="n">
+      <c r="G8" s="1" t="n">
         <v>0.01</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="H8" s="1" t="n">
         <v>0.42</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="I8" s="1" t="n">
         <v>0.6</v>
       </c>
-      <c r="I8" s="1" t="n">
+      <c r="J8" s="1" t="n">
         <v>105</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="K8" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="K8" s="1" t="n">
+      <c r="L8" s="1" t="n">
         <v>1.3</v>
       </c>
-      <c r="L8" s="1" t="n">
+      <c r="M8" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="M8" s="1" t="n">
+      <c r="N8" s="1" t="n">
         <v>1.05</v>
       </c>
     </row>
@@ -885,31 +915,31 @@
           <t>신화</t>
         </is>
       </c>
-      <c r="C9" s="1" t="inlineStr">
+      <c r="C9" s="1" t="n">
+        <v>1800006</v>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
         <is>
           <t>#d9786a</t>
         </is>
       </c>
-      <c r="D9" s="1" t="n">
+      <c r="E9" s="1" t="n">
         <v>1.85</v>
       </c>
-      <c r="E9" s="1" t="n">
+      <c r="F9" s="1" t="n">
         <v>1.2</v>
       </c>
-      <c r="F9" s="1" t="n">
+      <c r="G9" s="1" t="n">
         <v>0.00186</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="H9" s="1" t="n">
         <v>0.34</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="I9" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="I9" s="1" t="n">
+      <c r="J9" s="1" t="n">
         <v>189</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
         <v>0</v>
@@ -918,6 +948,9 @@
         <v>0</v>
       </c>
       <c r="M9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Data_Table/쥐 등급 테이블.xlsx
+++ b/Data_Table/쥐 등급 테이블.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Grade" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grade" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -686,7 +686,7 @@
         <v>1</v>
       </c>
       <c r="I4" s="1" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="J4" s="1" t="n">
         <v>10</v>
@@ -736,7 +736,7 @@
         <v>0.83</v>
       </c>
       <c r="I5" s="1" t="n">
-        <v>1.5</v>
+        <v>15</v>
       </c>
       <c r="J5" s="1" t="n">
         <v>18</v>
@@ -786,7 +786,7 @@
         <v>0.66</v>
       </c>
       <c r="I6" s="1" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J6" s="1" t="n">
         <v>32</v>
@@ -836,7 +836,7 @@
         <v>0.52</v>
       </c>
       <c r="I7" s="1" t="n">
-        <v>0.8</v>
+        <v>8</v>
       </c>
       <c r="J7" s="1" t="n">
         <v>58</v>
@@ -886,7 +886,7 @@
         <v>0.42</v>
       </c>
       <c r="I8" s="1" t="n">
-        <v>0.6</v>
+        <v>6</v>
       </c>
       <c r="J8" s="1" t="n">
         <v>105</v>
@@ -936,7 +936,7 @@
         <v>0.34</v>
       </c>
       <c r="I9" s="1" t="n">
-        <v>0.5</v>
+        <v>5</v>
       </c>
       <c r="J9" s="1" t="n">
         <v>189</v>
